--- a/avc/dist/20261025_奇鋐模型_v0.2.xlsx
+++ b/avc/dist/20261025_奇鋐模型_v0.2.xlsx
@@ -6190,7 +6190,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6408,7 +6408,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6529,7 +6529,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6650,7 +6650,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6771,7 +6771,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
@@ -6892,7 +6892,7 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">_v0.2.2.xlsx</t>
+      <t xml:space="preserve">_v0.3.xlsx</t>
     </r>
     <r>
       <rPr>
